--- a/spectra_2026/data/SpectralDataSpecies_notInSingleTip-MarleneReview-20260901.xlsx
+++ b/spectra_2026/data/SpectralDataSpecies_notInSingleTip-MarleneReview-20260901.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MHahn\Dropbox\Marlene Work Area\OaksWorld-SingleTip-Ruben_JCB_Kieran\Cavendar-Bares-2026-SpectralData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahipp\Documents\github\fagaceae-phylo\spectra_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9757CD-71B6-4C01-8D4D-BA5283EC9FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835B80FD-38A5-4DFD-AE17-E0BF772F45F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="2295" windowWidth="21840" windowHeight="13020" activeTab="3" xr2:uid="{1BAB3139-B2FE-4142-947A-295D6A02B330}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" firstSheet="1" activeTab="3" xr2:uid="{1BAB3139-B2FE-4142-947A-295D6A02B330}"/>
   </bookViews>
   <sheets>
     <sheet name="JCB-sp not found" sheetId="1" r:id="rId1"/>
@@ -2404,7 +2404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2414,6 +2414,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2750,14 +2759,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019F51C4-C042-4F8D-9A9A-BEA351C5556D}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="156.5703125" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="1" max="1" width="36.40625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="156.54296875" customWidth="1"/>
+    <col min="3" max="3" width="33.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
@@ -2768,7 +2777,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2776,7 +2785,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2787,7 +2796,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2798,7 +2807,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2809,7 +2818,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2820,7 +2829,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2831,7 +2840,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2842,7 +2851,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2853,7 +2862,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2864,7 +2873,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2875,7 +2884,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2886,7 +2895,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2897,7 +2906,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2908,7 +2917,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -2919,7 +2928,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2930,7 +2939,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2941,7 +2950,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2952,7 +2961,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -2963,7 +2972,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2974,7 +2983,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2985,7 +2994,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -2996,7 +3005,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -3007,7 +3016,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -3018,7 +3027,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -3029,7 +3038,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -3040,7 +3049,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -3051,7 +3060,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -3059,7 +3068,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -3070,7 +3079,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -3081,7 +3090,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -3092,7 +3101,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -3117,12 +3126,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC9483F-D3AF-41A5-B1B4-D4048BB54AFC}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>452</v>
       </c>
@@ -3130,182 +3139,182 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B16" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B24" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B27" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B31" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B32" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B33" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B34" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B36" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.75">
       <c r="B37" t="s">
         <v>30</v>
       </c>
@@ -3319,15 +3328,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81550214-B5A3-4014-BB07-DC8138CAC134}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:E353"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="46.28515625" customWidth="1"/>
+    <col min="1" max="1" width="46.26953125" customWidth="1"/>
     <col min="2" max="2" width="24" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -3338,7 +3347,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>260</v>
       </c>
@@ -3347,7 +3356,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>367</v>
       </c>
@@ -3356,7 +3365,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>366</v>
       </c>
@@ -3365,7 +3374,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>242</v>
       </c>
@@ -3374,7 +3383,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>296</v>
       </c>
@@ -3383,7 +3392,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>263</v>
       </c>
@@ -3392,7 +3401,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -3401,7 +3410,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>241</v>
       </c>
@@ -3410,7 +3419,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>262</v>
       </c>
@@ -3419,7 +3428,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>289</v>
       </c>
@@ -3428,7 +3437,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>419</v>
       </c>
@@ -3440,7 +3449,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>187</v>
       </c>
@@ -3449,7 +3458,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>234</v>
       </c>
@@ -3458,7 +3467,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>246</v>
       </c>
@@ -3467,7 +3476,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>124</v>
       </c>
@@ -3476,7 +3485,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>277</v>
       </c>
@@ -3485,7 +3494,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>323</v>
       </c>
@@ -3494,7 +3503,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>345</v>
       </c>
@@ -3506,7 +3515,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>390</v>
       </c>
@@ -3518,7 +3527,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>310</v>
       </c>
@@ -3527,7 +3536,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>341</v>
       </c>
@@ -3536,7 +3545,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>292</v>
       </c>
@@ -3545,7 +3554,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>293</v>
       </c>
@@ -3557,7 +3566,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>151</v>
       </c>
@@ -3566,7 +3575,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>109</v>
       </c>
@@ -3575,7 +3584,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>88</v>
       </c>
@@ -3584,7 +3593,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>347</v>
       </c>
@@ -3593,7 +3602,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -3602,7 +3611,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>377</v>
       </c>
@@ -3611,7 +3620,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>276</v>
       </c>
@@ -3620,7 +3629,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>231</v>
       </c>
@@ -3629,7 +3638,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>217</v>
       </c>
@@ -3638,7 +3647,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>374</v>
       </c>
@@ -3647,7 +3656,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>350</v>
       </c>
@@ -3656,7 +3665,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -3665,7 +3674,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>181</v>
       </c>
@@ -3674,7 +3683,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>320</v>
       </c>
@@ -3683,7 +3692,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>255</v>
       </c>
@@ -3692,7 +3701,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -3701,7 +3710,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -3710,7 +3719,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>243</v>
       </c>
@@ -3719,7 +3728,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>317</v>
       </c>
@@ -3728,7 +3737,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>285</v>
       </c>
@@ -3737,7 +3746,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>417</v>
       </c>
@@ -3746,7 +3755,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>404</v>
       </c>
@@ -3755,7 +3764,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>244</v>
       </c>
@@ -3764,7 +3773,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>338</v>
       </c>
@@ -3773,7 +3782,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>146</v>
       </c>
@@ -3782,7 +3791,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -3791,7 +3800,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>215</v>
       </c>
@@ -3800,7 +3809,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>274</v>
       </c>
@@ -3809,7 +3818,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>186</v>
       </c>
@@ -3818,7 +3827,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>210</v>
       </c>
@@ -3827,7 +3836,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>270</v>
       </c>
@@ -3836,7 +3845,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>375</v>
       </c>
@@ -3845,7 +3854,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>180</v>
       </c>
@@ -3854,7 +3863,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>361</v>
       </c>
@@ -3863,7 +3872,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>271</v>
       </c>
@@ -3872,7 +3881,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>70</v>
       </c>
@@ -3881,7 +3890,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>149</v>
       </c>
@@ -3890,7 +3899,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>199</v>
       </c>
@@ -3899,7 +3908,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>391</v>
       </c>
@@ -3908,7 +3917,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>121</v>
       </c>
@@ -3917,7 +3926,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>324</v>
       </c>
@@ -3926,7 +3935,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>332</v>
       </c>
@@ -3935,7 +3944,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>291</v>
       </c>
@@ -3944,7 +3953,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>265</v>
       </c>
@@ -3953,7 +3962,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>389</v>
       </c>
@@ -3965,7 +3974,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>384</v>
       </c>
@@ -3977,7 +3986,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>352</v>
       </c>
@@ -3986,7 +3995,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>311</v>
       </c>
@@ -3998,7 +4007,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>398</v>
       </c>
@@ -4010,7 +4019,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>226</v>
       </c>
@@ -4019,7 +4028,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>225</v>
       </c>
@@ -4028,7 +4037,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -4037,7 +4046,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>322</v>
       </c>
@@ -4046,7 +4055,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>305</v>
       </c>
@@ -4055,7 +4064,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>230</v>
       </c>
@@ -4064,7 +4073,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>107</v>
       </c>
@@ -4073,7 +4082,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>334</v>
       </c>
@@ -4082,7 +4091,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>212</v>
       </c>
@@ -4091,7 +4100,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>273</v>
       </c>
@@ -4100,7 +4109,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>405</v>
       </c>
@@ -4109,7 +4118,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -4118,7 +4127,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>369</v>
       </c>
@@ -4127,7 +4136,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>298</v>
       </c>
@@ -4136,7 +4145,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -4145,7 +4154,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>287</v>
       </c>
@@ -4154,7 +4163,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>362</v>
       </c>
@@ -4166,7 +4175,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>396</v>
       </c>
@@ -4175,7 +4184,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>280</v>
       </c>
@@ -4184,7 +4193,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>169</v>
       </c>
@@ -4193,7 +4202,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
         <v>164</v>
       </c>
@@ -4202,7 +4211,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A95" t="s">
         <v>286</v>
       </c>
@@ -4211,7 +4220,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>74</v>
       </c>
@@ -4220,7 +4229,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A97" t="s">
         <v>72</v>
       </c>
@@ -4229,7 +4238,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A98" t="s">
         <v>129</v>
       </c>
@@ -4238,7 +4247,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A99" t="s">
         <v>353</v>
       </c>
@@ -4247,7 +4256,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A100" t="s">
         <v>247</v>
       </c>
@@ -4256,7 +4265,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A101" t="s">
         <v>223</v>
       </c>
@@ -4265,7 +4274,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A102" t="s">
         <v>173</v>
       </c>
@@ -4274,7 +4283,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A103" t="s">
         <v>278</v>
       </c>
@@ -4283,7 +4292,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A104" t="s">
         <v>349</v>
       </c>
@@ -4292,7 +4301,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A105" t="s">
         <v>160</v>
       </c>
@@ -4301,7 +4310,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="106" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A106" t="s">
         <v>257</v>
       </c>
@@ -4310,7 +4319,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="107" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A107" t="s">
         <v>144</v>
       </c>
@@ -4319,7 +4328,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="108" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A108" t="s">
         <v>288</v>
       </c>
@@ -4328,7 +4337,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="109" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A109" t="s">
         <v>134</v>
       </c>
@@ -4337,7 +4346,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="110" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A110" t="s">
         <v>191</v>
       </c>
@@ -4346,7 +4355,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A111" t="s">
         <v>152</v>
       </c>
@@ -4355,7 +4364,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="112" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A112" t="s">
         <v>297</v>
       </c>
@@ -4364,7 +4373,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A113" t="s">
         <v>162</v>
       </c>
@@ -4373,7 +4382,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A114" t="s">
         <v>346</v>
       </c>
@@ -4385,7 +4394,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A115" t="s">
         <v>306</v>
       </c>
@@ -4397,7 +4406,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A116" t="s">
         <v>89</v>
       </c>
@@ -4406,7 +4415,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A117" t="s">
         <v>128</v>
       </c>
@@ -4415,7 +4424,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A118" t="s">
         <v>102</v>
       </c>
@@ -4424,7 +4433,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A119" t="s">
         <v>141</v>
       </c>
@@ -4433,7 +4442,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A120" t="s">
         <v>249</v>
       </c>
@@ -4442,7 +4451,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A121" t="s">
         <v>163</v>
       </c>
@@ -4451,7 +4460,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A122" t="s">
         <v>406</v>
       </c>
@@ -4460,7 +4469,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A123" t="s">
         <v>200</v>
       </c>
@@ -4469,7 +4478,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A124" t="s">
         <v>272</v>
       </c>
@@ -4478,7 +4487,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A125" t="s">
         <v>201</v>
       </c>
@@ -4490,7 +4499,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A126" t="s">
         <v>96</v>
       </c>
@@ -4499,7 +4508,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A127" t="s">
         <v>220</v>
       </c>
@@ -4508,7 +4517,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A128" t="s">
         <v>318</v>
       </c>
@@ -4517,7 +4526,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A129" t="s">
         <v>328</v>
       </c>
@@ -4526,7 +4535,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A130" t="s">
         <v>238</v>
       </c>
@@ -4535,7 +4544,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A131" t="s">
         <v>354</v>
       </c>
@@ -4544,7 +4553,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A132" t="s">
         <v>300</v>
       </c>
@@ -4553,7 +4562,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A133" t="s">
         <v>211</v>
       </c>
@@ -4562,7 +4571,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A134" t="s">
         <v>388</v>
       </c>
@@ -4571,7 +4580,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A135" t="s">
         <v>93</v>
       </c>
@@ -4583,7 +4592,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A136" t="s">
         <v>290</v>
       </c>
@@ -4592,7 +4601,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A137" s="5" t="s">
         <v>136</v>
       </c>
@@ -4605,7 +4614,7 @@
       </c>
       <c r="D137" s="5"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A138" t="s">
         <v>282</v>
       </c>
@@ -4617,7 +4626,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A139" t="s">
         <v>205</v>
       </c>
@@ -4626,7 +4635,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A140" t="s">
         <v>157</v>
       </c>
@@ -4635,7 +4644,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A141" t="s">
         <v>196</v>
       </c>
@@ -4644,7 +4653,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -4653,7 +4662,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A143" t="s">
         <v>248</v>
       </c>
@@ -4662,7 +4671,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.75">
       <c r="A144" t="s">
         <v>174</v>
       </c>
@@ -4671,7 +4680,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A145" t="s">
         <v>378</v>
       </c>
@@ -4683,7 +4692,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A146" t="s">
         <v>127</v>
       </c>
@@ -4692,7 +4701,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A147" t="s">
         <v>120</v>
       </c>
@@ -4701,7 +4710,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A148" t="s">
         <v>202</v>
       </c>
@@ -4710,7 +4719,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A149" t="s">
         <v>119</v>
       </c>
@@ -4719,7 +4728,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A150" t="s">
         <v>145</v>
       </c>
@@ -4728,7 +4737,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A151" t="s">
         <v>140</v>
       </c>
@@ -4737,7 +4746,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A152" t="s">
         <v>203</v>
       </c>
@@ -4746,7 +4755,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A153" t="s">
         <v>105</v>
       </c>
@@ -4755,7 +4764,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A154" t="s">
         <v>330</v>
       </c>
@@ -4764,7 +4773,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A155" s="5" t="s">
         <v>402</v>
       </c>
@@ -4776,7 +4785,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A156" t="s">
         <v>325</v>
       </c>
@@ -4785,7 +4794,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A157" t="s">
         <v>364</v>
       </c>
@@ -4794,7 +4803,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A158" t="s">
         <v>193</v>
       </c>
@@ -4803,7 +4812,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A159" t="s">
         <v>131</v>
       </c>
@@ -4812,7 +4821,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A160" t="s">
         <v>304</v>
       </c>
@@ -4821,7 +4830,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A161" t="s">
         <v>344</v>
       </c>
@@ -4830,7 +4839,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A162" t="s">
         <v>218</v>
       </c>
@@ -4839,7 +4848,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A163" t="s">
         <v>106</v>
       </c>
@@ -4848,7 +4857,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A164" s="5" t="s">
         <v>394</v>
       </c>
@@ -4860,7 +4869,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A165" t="s">
         <v>380</v>
       </c>
@@ -4869,7 +4878,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A166" t="s">
         <v>266</v>
       </c>
@@ -4878,7 +4887,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A167" t="s">
         <v>321</v>
       </c>
@@ -4887,7 +4896,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A168" t="s">
         <v>195</v>
       </c>
@@ -4896,7 +4905,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A169" t="s">
         <v>130</v>
       </c>
@@ -4905,7 +4914,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A170" t="s">
         <v>90</v>
       </c>
@@ -4914,7 +4923,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A171" t="s">
         <v>194</v>
       </c>
@@ -4923,7 +4932,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A172" t="s">
         <v>329</v>
       </c>
@@ -4932,7 +4941,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A173" t="s">
         <v>379</v>
       </c>
@@ -4941,7 +4950,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A174" t="s">
         <v>112</v>
       </c>
@@ -4950,7 +4959,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A175" t="s">
         <v>166</v>
       </c>
@@ -4959,7 +4968,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A176" t="s">
         <v>373</v>
       </c>
@@ -4968,7 +4977,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="177" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A177" t="s">
         <v>355</v>
       </c>
@@ -4977,7 +4986,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="178" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A178" t="s">
         <v>268</v>
       </c>
@@ -4986,7 +4995,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="179" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A179" t="s">
         <v>335</v>
       </c>
@@ -4995,7 +5004,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="180" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A180" t="s">
         <v>281</v>
       </c>
@@ -5004,7 +5013,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="181" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A181" t="s">
         <v>309</v>
       </c>
@@ -5013,7 +5022,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="182" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A182" t="s">
         <v>154</v>
       </c>
@@ -5022,7 +5031,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="183" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A183" t="s">
         <v>213</v>
       </c>
@@ -5031,7 +5040,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="184" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A184" t="s">
         <v>407</v>
       </c>
@@ -5040,7 +5049,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="185" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A185" t="s">
         <v>408</v>
       </c>
@@ -5049,7 +5058,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="186" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A186" t="s">
         <v>331</v>
       </c>
@@ -5058,7 +5067,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="187" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A187" t="s">
         <v>229</v>
       </c>
@@ -5067,7 +5076,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="188" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A188" t="s">
         <v>183</v>
       </c>
@@ -5076,7 +5085,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="189" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A189" t="s">
         <v>139</v>
       </c>
@@ -5085,7 +5094,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="190" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A190" t="s">
         <v>267</v>
       </c>
@@ -5094,7 +5103,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="191" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A191" t="s">
         <v>224</v>
       </c>
@@ -5103,7 +5112,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="192" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A192" t="s">
         <v>386</v>
       </c>
@@ -5112,7 +5121,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="193" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A193" t="s">
         <v>165</v>
       </c>
@@ -5121,7 +5130,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="194" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A194" t="s">
         <v>254</v>
       </c>
@@ -5130,7 +5139,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="195" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A195" t="s">
         <v>113</v>
       </c>
@@ -5139,7 +5148,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="196" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A196" t="s">
         <v>126</v>
       </c>
@@ -5148,7 +5157,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="197" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A197" t="s">
         <v>387</v>
       </c>
@@ -5157,7 +5166,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="198" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A198" t="s">
         <v>381</v>
       </c>
@@ -5166,7 +5175,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="199" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A199" t="s">
         <v>185</v>
       </c>
@@ -5175,7 +5184,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="200" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A200" t="s">
         <v>117</v>
       </c>
@@ -5184,7 +5193,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="201" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A201" t="s">
         <v>409</v>
       </c>
@@ -5193,7 +5202,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="202" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A202" t="s">
         <v>256</v>
       </c>
@@ -5202,7 +5211,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="203" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A203" t="s">
         <v>150</v>
       </c>
@@ -5211,7 +5220,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="204" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A204" t="s">
         <v>235</v>
       </c>
@@ -5220,7 +5229,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="205" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A205" t="s">
         <v>269</v>
       </c>
@@ -5229,7 +5238,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="206" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A206" t="s">
         <v>340</v>
       </c>
@@ -5238,7 +5247,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="207" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A207" t="s">
         <v>326</v>
       </c>
@@ -5247,7 +5256,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="208" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A208" t="s">
         <v>84</v>
       </c>
@@ -5256,7 +5265,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A209" t="s">
         <v>376</v>
       </c>
@@ -5265,7 +5274,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A210" t="s">
         <v>342</v>
       </c>
@@ -5274,7 +5283,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A211" t="s">
         <v>189</v>
       </c>
@@ -5286,7 +5295,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A212" t="s">
         <v>77</v>
       </c>
@@ -5295,7 +5304,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A213" t="s">
         <v>275</v>
       </c>
@@ -5304,7 +5313,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A214" t="s">
         <v>71</v>
       </c>
@@ -5313,7 +5322,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A215" t="s">
         <v>147</v>
       </c>
@@ -5322,7 +5331,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A216" t="s">
         <v>82</v>
       </c>
@@ -5331,7 +5340,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A217" t="s">
         <v>392</v>
       </c>
@@ -5343,7 +5352,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A218" t="s">
         <v>410</v>
       </c>
@@ -5352,7 +5361,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A219" t="s">
         <v>339</v>
       </c>
@@ -5361,7 +5370,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A220" t="s">
         <v>313</v>
       </c>
@@ -5376,7 +5385,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A221" t="s">
         <v>371</v>
       </c>
@@ -5385,7 +5394,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A222" t="s">
         <v>413</v>
       </c>
@@ -5397,7 +5406,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A223" t="s">
         <v>138</v>
       </c>
@@ -5406,7 +5415,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.75">
       <c r="A224" t="s">
         <v>75</v>
       </c>
@@ -5415,7 +5424,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A225" t="s">
         <v>356</v>
       </c>
@@ -5424,7 +5433,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A226" t="s">
         <v>206</v>
       </c>
@@ -5433,7 +5442,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A227" t="s">
         <v>397</v>
       </c>
@@ -5442,7 +5451,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A228" t="s">
         <v>148</v>
       </c>
@@ -5451,7 +5460,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A229" t="s">
         <v>100</v>
       </c>
@@ -5460,7 +5469,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A230" t="s">
         <v>382</v>
       </c>
@@ -5469,7 +5478,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A231" t="s">
         <v>258</v>
       </c>
@@ -5478,7 +5487,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A232" t="s">
         <v>79</v>
       </c>
@@ -5487,7 +5496,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A233" t="s">
         <v>98</v>
       </c>
@@ -5496,7 +5505,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A234" t="s">
         <v>192</v>
       </c>
@@ -5508,7 +5517,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A235" t="s">
         <v>227</v>
       </c>
@@ -5517,7 +5526,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A236" t="s">
         <v>114</v>
       </c>
@@ -5526,7 +5535,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A237" t="s">
         <v>122</v>
       </c>
@@ -5535,7 +5544,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A238" t="s">
         <v>179</v>
       </c>
@@ -5544,7 +5553,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A239" t="s">
         <v>348</v>
       </c>
@@ -5553,7 +5562,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A240" t="s">
         <v>108</v>
       </c>
@@ -5562,7 +5571,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A241" t="s">
         <v>125</v>
       </c>
@@ -5571,7 +5580,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A242" t="s">
         <v>161</v>
       </c>
@@ -5580,7 +5589,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A243" t="s">
         <v>99</v>
       </c>
@@ -5589,7 +5598,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A244" t="s">
         <v>208</v>
       </c>
@@ -5598,7 +5607,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A245" t="s">
         <v>216</v>
       </c>
@@ -5607,7 +5616,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A246" t="s">
         <v>221</v>
       </c>
@@ -5616,7 +5625,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A247" t="s">
         <v>132</v>
       </c>
@@ -5625,7 +5634,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A248" t="s">
         <v>76</v>
       </c>
@@ -5634,7 +5643,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A249" t="s">
         <v>137</v>
       </c>
@@ -5643,7 +5652,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A250" t="s">
         <v>78</v>
       </c>
@@ -5652,7 +5661,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A251" t="s">
         <v>259</v>
       </c>
@@ -5661,7 +5670,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A252" t="s">
         <v>135</v>
       </c>
@@ -5670,7 +5679,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A253" t="s">
         <v>294</v>
       </c>
@@ -5679,7 +5688,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A254" t="s">
         <v>295</v>
       </c>
@@ -5691,7 +5700,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A255" t="s">
         <v>222</v>
       </c>
@@ -5700,7 +5709,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A256" t="s">
         <v>403</v>
       </c>
@@ -5712,7 +5721,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="257" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A257" t="s">
         <v>123</v>
       </c>
@@ -5721,7 +5730,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="258" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A258" t="s">
         <v>283</v>
       </c>
@@ -5730,7 +5739,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="259" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A259" t="s">
         <v>308</v>
       </c>
@@ -5739,7 +5748,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="260" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -5748,7 +5757,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="261" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A261" t="s">
         <v>80</v>
       </c>
@@ -5757,7 +5766,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="262" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A262" t="s">
         <v>252</v>
       </c>
@@ -5766,7 +5775,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="263" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A263" t="s">
         <v>178</v>
       </c>
@@ -5775,7 +5784,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="264" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A264" t="s">
         <v>240</v>
       </c>
@@ -5784,7 +5793,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="265" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A265" t="s">
         <v>171</v>
       </c>
@@ -5793,7 +5802,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="266" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A266" t="s">
         <v>204</v>
       </c>
@@ -5802,7 +5811,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="267" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A267" t="s">
         <v>253</v>
       </c>
@@ -5811,7 +5820,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="268" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A268" t="s">
         <v>175</v>
       </c>
@@ -5820,7 +5829,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="269" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A269" t="s">
         <v>182</v>
       </c>
@@ -5829,7 +5838,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="270" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A270" t="s">
         <v>395</v>
       </c>
@@ -5838,7 +5847,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="271" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A271" t="s">
         <v>118</v>
       </c>
@@ -5847,7 +5856,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="272" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A272" t="s">
         <v>370</v>
       </c>
@@ -5856,7 +5865,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="273" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A273" t="s">
         <v>92</v>
       </c>
@@ -5865,7 +5874,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="274" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A274" t="s">
         <v>188</v>
       </c>
@@ -5874,7 +5883,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="275" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A275" t="s">
         <v>115</v>
       </c>
@@ -5883,7 +5892,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="276" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A276" t="s">
         <v>143</v>
       </c>
@@ -5892,7 +5901,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="277" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A277" t="s">
         <v>337</v>
       </c>
@@ -5901,7 +5910,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="278" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A278" t="s">
         <v>177</v>
       </c>
@@ -5910,7 +5919,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="279" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A279" t="s">
         <v>312</v>
       </c>
@@ -5919,7 +5928,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="280" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A280" t="s">
         <v>237</v>
       </c>
@@ -5928,7 +5937,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="281" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A281" t="s">
         <v>156</v>
       </c>
@@ -5937,7 +5946,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="282" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A282" t="s">
         <v>214</v>
       </c>
@@ -5946,7 +5955,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="283" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A283" t="s">
         <v>86</v>
       </c>
@@ -5955,7 +5964,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="284" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A284" t="s">
         <v>86</v>
       </c>
@@ -5964,7 +5973,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="285" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A285" t="s">
         <v>343</v>
       </c>
@@ -5973,7 +5982,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="286" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A286" t="s">
         <v>184</v>
       </c>
@@ -5982,7 +5991,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="287" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A287" t="s">
         <v>385</v>
       </c>
@@ -5991,7 +6000,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="288" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A288" t="s">
         <v>357</v>
       </c>
@@ -6000,7 +6009,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A289" t="s">
         <v>87</v>
       </c>
@@ -6009,7 +6018,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A290" t="s">
         <v>69</v>
       </c>
@@ -6018,7 +6027,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A291" t="s">
         <v>358</v>
       </c>
@@ -6027,7 +6036,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A292" t="s">
         <v>197</v>
       </c>
@@ -6036,7 +6045,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A293" t="s">
         <v>415</v>
       </c>
@@ -6048,7 +6057,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A294" t="s">
         <v>209</v>
       </c>
@@ -6057,7 +6066,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A295" t="s">
         <v>363</v>
       </c>
@@ -6066,7 +6075,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A296" t="s">
         <v>351</v>
       </c>
@@ -6075,7 +6084,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A297" t="s">
         <v>167</v>
       </c>
@@ -6084,7 +6093,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A298" t="s">
         <v>172</v>
       </c>
@@ -6093,7 +6102,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A299" t="s">
         <v>219</v>
       </c>
@@ -6102,7 +6111,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A300" t="s">
         <v>73</v>
       </c>
@@ -6111,7 +6120,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A301" t="s">
         <v>359</v>
       </c>
@@ -6120,7 +6129,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A302" t="s">
         <v>168</v>
       </c>
@@ -6129,7 +6138,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A303" t="s">
         <v>319</v>
       </c>
@@ -6138,7 +6147,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A304" t="s">
         <v>233</v>
       </c>
@@ -6147,7 +6156,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A305" t="s">
         <v>284</v>
       </c>
@@ -6156,7 +6165,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A306" t="s">
         <v>228</v>
       </c>
@@ -6165,7 +6174,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A307" t="s">
         <v>336</v>
       </c>
@@ -6174,7 +6183,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A308" t="s">
         <v>91</v>
       </c>
@@ -6183,7 +6192,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A309" t="s">
         <v>383</v>
       </c>
@@ -6192,7 +6201,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A310" t="s">
         <v>232</v>
       </c>
@@ -6201,7 +6210,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A311" t="s">
         <v>303</v>
       </c>
@@ -6210,7 +6219,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A312" t="s">
         <v>198</v>
       </c>
@@ -6219,7 +6228,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A313" t="s">
         <v>399</v>
       </c>
@@ -6231,7 +6240,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A314" t="s">
         <v>302</v>
       </c>
@@ -6243,7 +6252,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A315" t="s">
         <v>365</v>
       </c>
@@ -6255,7 +6264,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A316" t="s">
         <v>333</v>
       </c>
@@ -6264,7 +6273,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A317" t="s">
         <v>411</v>
       </c>
@@ -6273,7 +6282,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A318" t="s">
         <v>97</v>
       </c>
@@ -6282,7 +6291,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A319" t="s">
         <v>316</v>
       </c>
@@ -6294,7 +6303,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A320" t="s">
         <v>315</v>
       </c>
@@ -6306,7 +6315,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A321" t="s">
         <v>314</v>
       </c>
@@ -6318,7 +6327,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A322" t="s">
         <v>245</v>
       </c>
@@ -6327,7 +6336,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A323" t="s">
         <v>307</v>
       </c>
@@ -6336,7 +6345,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A324" t="s">
         <v>264</v>
       </c>
@@ -6345,7 +6354,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A325" t="s">
         <v>299</v>
       </c>
@@ -6354,7 +6363,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A326" t="s">
         <v>368</v>
       </c>
@@ -6363,7 +6372,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A327" t="s">
         <v>393</v>
       </c>
@@ -6375,7 +6384,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A328" t="s">
         <v>414</v>
       </c>
@@ -6387,7 +6396,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A329" t="s">
         <v>412</v>
       </c>
@@ -6396,7 +6405,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A330" t="s">
         <v>176</v>
       </c>
@@ -6405,7 +6414,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A331" t="s">
         <v>133</v>
       </c>
@@ -6414,7 +6423,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A332" t="s">
         <v>104</v>
       </c>
@@ -6423,7 +6432,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A333" t="s">
         <v>159</v>
       </c>
@@ -6435,7 +6444,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A334" t="s">
         <v>401</v>
       </c>
@@ -6444,7 +6453,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A335" t="s">
         <v>279</v>
       </c>
@@ -6453,7 +6462,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A336" t="s">
         <v>416</v>
       </c>
@@ -6462,7 +6471,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A337" t="s">
         <v>372</v>
       </c>
@@ -6471,7 +6480,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A338" t="s">
         <v>103</v>
       </c>
@@ -6480,7 +6489,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A339" t="s">
         <v>418</v>
       </c>
@@ -6492,7 +6501,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A340" t="s">
         <v>251</v>
       </c>
@@ -6501,7 +6510,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A341" t="s">
         <v>158</v>
       </c>
@@ -6510,7 +6519,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A342" t="s">
         <v>153</v>
       </c>
@@ -6519,7 +6528,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A343" t="s">
         <v>236</v>
       </c>
@@ -6528,7 +6537,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A344" t="s">
         <v>142</v>
       </c>
@@ -6537,7 +6546,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A345" t="s">
         <v>83</v>
       </c>
@@ -6546,7 +6555,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A346" t="s">
         <v>400</v>
       </c>
@@ -6555,7 +6564,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A347" t="s">
         <v>301</v>
       </c>
@@ -6564,7 +6573,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A348" t="s">
         <v>207</v>
       </c>
@@ -6573,7 +6582,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A349" t="s">
         <v>327</v>
       </c>
@@ -6582,7 +6591,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A350" t="s">
         <v>155</v>
       </c>
@@ -6591,7 +6600,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A351" t="s">
         <v>360</v>
       </c>
@@ -6600,7 +6609,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.75">
       <c r="A352" t="s">
         <v>250</v>
       </c>
@@ -6609,7 +6618,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="353" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" hidden="1" x14ac:dyDescent="0.75">
       <c r="A353" t="s">
         <v>239</v>
       </c>
@@ -6637,15 +6646,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525EB1CC-32EB-452C-B51E-040402F5231E}">
   <dimension ref="A1:D323"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="108.5703125" customWidth="1"/>
+    <col min="1" max="1" width="37.40625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.04296875" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="75.6328125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>751</v>
       </c>
@@ -6655,404 +6664,404 @@
       <c r="C1" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="9" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A2" s="7" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A3" s="7" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A4" s="7" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A5" s="7" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A6" s="7" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A7" s="7" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A8" s="7" t="s">
         <v>459</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A9" s="7" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A10" s="7" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A11" s="7" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A12" s="7" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A13" s="7" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A14" s="7" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A15" s="7" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A16" s="7" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" s="7" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" s="7" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" s="7" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20" s="7" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A21" s="7" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A22" s="7" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A23" s="7" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A24" s="7" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A25" s="7" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A26" s="7" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A27" s="7" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A28" s="7" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A29" s="7" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A30" s="7" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A31" s="7" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A32" s="7" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A33" s="7" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A34" s="7" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A35" s="7" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A36" s="7" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A37" s="7" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A38" s="7" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A39" s="7" t="s">
         <v>490</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A40" s="7" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A41" s="7" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A42" s="7" t="s">
         <v>493</v>
       </c>
       <c r="B42" t="s">
         <v>18</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A43" s="7" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A44" s="7" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A45" s="7" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A46" s="7" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A47" s="7" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A48" s="7" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A49" s="7" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A50" s="7" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A51" s="7" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A52" s="7" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A53" s="7" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A54" s="7" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A55" s="7" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A56" s="7" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A57" s="7" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A58" s="7" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A59" s="7" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A60" s="7" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A61" s="7" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A62" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A63" s="7" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A64" s="7" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A65" s="7" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A66" s="7" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A67" s="7" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A68" s="7" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A69" s="7" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A70" s="7" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A71" s="7" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A72" s="7" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A73" s="7" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A74" s="7" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A75" s="7" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A76" s="7" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A77" s="7" t="s">
         <v>528</v>
       </c>
@@ -7060,32 +7069,32 @@
         <v>450</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A78" s="7" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A79" s="7" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A80" s="7" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A81" s="7" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A82" s="7" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A83" s="7" t="s">
         <v>534</v>
       </c>
@@ -7093,695 +7102,695 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A84" s="7" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A85" s="7" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A86" s="7" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A87" s="7" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A88" s="7" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A89" s="7" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A90" s="7" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A91" s="7" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A92" s="7" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A93" s="7" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A94" s="7" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A95" s="7" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A96" s="7" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A97" s="7" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A98" s="7" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A99" s="7" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A100" s="7" t="s">
         <v>551</v>
       </c>
       <c r="B100" t="s">
         <v>23</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A101" s="7" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A102" s="7" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A103" s="7" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A104" s="7" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A105" s="7" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A106" s="7" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A107" s="7" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A108" s="7" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A109" s="7" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A110" s="7" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A111" s="7" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A112" s="7" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A113" s="7" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A114" s="7" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A115" s="7" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A116" s="7" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A117" s="7" t="s">
         <v>568</v>
       </c>
       <c r="B117" t="s">
         <v>445</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="10" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A118" s="7" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A119" s="7" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A120" s="7" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A121" s="7" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A122" s="7" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A123" s="7" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A124" s="7" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A125" s="7" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A126" s="7" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A127" s="7" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A128" s="7" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A129" s="7" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A130" s="7" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A131" s="7" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A132" s="7" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A133" s="7" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A134" s="7" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A135" s="7" t="s">
         <v>584</v>
       </c>
       <c r="B135" t="s">
         <v>448</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="10" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A136" s="7" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A137" s="7" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A138" s="7" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A139" s="7" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A140" s="7" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A141" s="7" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A142" s="7" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A143" s="7" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A144" s="7" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A145" s="7" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A146" s="7" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A147" s="7" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A148" s="7" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A149" s="7" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A150" s="7" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A151" s="7" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A152" s="7" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A153" s="7" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A154" s="7" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A155" s="7" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A156" s="7" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A157" s="7" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A158" s="7" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A159" s="7" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A160" s="7" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A161" s="7" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A162" s="7" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A163" s="7" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A164" s="7" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A165" s="7" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A166" s="7" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A167" s="7" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A168" s="7" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A169" s="7" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A170" s="7" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A171" s="7" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A172" s="7" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A173" s="7" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A174" s="7" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A175" s="7" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A176" s="7" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A177" s="7" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A178" s="7" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A179" s="7" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A180" s="7" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A181" s="7" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A182" s="7" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A183" s="7" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A184" s="7" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A185" s="7" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A186" s="7" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A187" s="7" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A188" s="7" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A189" s="7" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A190" s="7" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A191" s="7" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A192" s="7" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A193" s="7" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A194" s="7" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A195" s="7" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A196" s="7" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A197" s="7" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A198" s="7" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A199" s="7" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A200" s="7" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A201" s="7" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A202" s="7" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A203" s="7" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A204" s="7" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A205" s="7" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A206" s="7" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A207" s="7" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A208" s="7" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A209" s="7" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A210" s="7" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A211" s="7" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A212" s="7" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A213" s="7" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A214" s="7" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A215" s="7" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A216" s="7" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A217" s="7" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" ht="73.75" x14ac:dyDescent="0.75">
       <c r="A218" s="7" t="s">
         <v>664</v>
       </c>
@@ -7791,185 +7800,185 @@
       <c r="C218" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D218" t="s">
+      <c r="D218" s="10" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A219" s="7" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A220" s="7" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A221" s="7" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A222" s="7" t="s">
         <v>668</v>
       </c>
       <c r="B222" t="s">
         <v>4</v>
       </c>
-      <c r="D222" t="s">
+      <c r="D222" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A223" s="7" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A224" s="7" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A225" s="7" t="s">
         <v>671</v>
       </c>
       <c r="B225" t="s">
         <v>26</v>
       </c>
-      <c r="D225" t="s">
+      <c r="D225" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A226" s="7" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A227" s="7" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A228" s="7" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A229" s="7" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A230" s="7" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A231" s="7" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A232" s="7" t="s">
         <v>678</v>
       </c>
       <c r="C232" t="s">
         <v>17</v>
       </c>
-      <c r="D232" t="s">
+      <c r="D232" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A233" s="7" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A234" s="7" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A235" s="7" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A236" s="7" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A237" s="7" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A238" s="7" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A239" s="7" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A240" s="7" t="s">
         <v>686</v>
       </c>
       <c r="B240" t="s">
         <v>5</v>
       </c>
-      <c r="D240" t="s">
+      <c r="D240" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A241" s="7" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A242" s="7" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A243" s="7" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A244" s="7" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A245" s="7" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A246" s="7" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A247" s="7" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A248" s="7" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A249" s="7" t="s">
         <v>695</v>
       </c>
@@ -7977,232 +7986,232 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A250" s="7" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A251" s="7" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A252" s="7" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A253" s="7" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A254" s="7" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A255" s="7" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A256" s="7" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A257" s="7" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A258" s="7" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A259" s="7" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A260" s="7" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A261" s="7" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A262" s="7" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A263" s="7" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A264" s="7" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A265" s="7" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A266" s="7" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A267" s="7" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A268" s="7" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A269" s="7" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A270" s="7" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A271" s="7" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A272" s="7" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A273" s="7" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A274" s="7" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A275" s="7" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A276" s="7" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A277" s="7" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A278" s="7" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A279" s="7" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A280" s="7" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A281" s="7" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A282" s="7" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A283" s="7" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A284" s="7" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A285" s="7" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A286" s="7" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A287" s="7" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A288" s="7" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A289" s="7" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A290" s="7" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A291" s="7" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A292" s="7" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A293" s="7" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A294" s="7" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A295" s="7" t="s">
         <v>741</v>
       </c>
@@ -8210,7 +8219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A296" s="7" t="s">
         <v>742</v>
       </c>
@@ -8218,195 +8227,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A297" s="7" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A298" s="7" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A299" s="7" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A300" s="7" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A301" s="7" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A302" s="7" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A303" s="7" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A304" s="7" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="305" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C305" t="s">
         <v>0</v>
       </c>
-      <c r="D305" t="s">
+      <c r="D305" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="306" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C306" t="s">
         <v>1</v>
       </c>
-      <c r="D306" t="s">
+      <c r="D306" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="307" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C307" t="s">
         <v>444</v>
       </c>
-      <c r="D307" t="s">
+      <c r="D307" s="10" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="308" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:4" ht="44.25" x14ac:dyDescent="0.75">
       <c r="C308" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D308" s="8" t="s">
+      <c r="D308" s="11" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="309" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C309" t="s">
         <v>8</v>
       </c>
-      <c r="D309" t="s">
+      <c r="D309" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="310" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C310" t="s">
         <v>9</v>
       </c>
-      <c r="D310" t="s">
+      <c r="D310" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="311" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C311" t="s">
         <v>446</v>
       </c>
-      <c r="D311" t="s">
+      <c r="D311" s="10" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="312" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C312" t="s">
         <v>10</v>
       </c>
-      <c r="D312" t="s">
+      <c r="D312" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="313" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C313" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D313" s="8" t="s">
+      <c r="D313" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="314" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C314" t="s">
         <v>13</v>
       </c>
-      <c r="D314" t="s">
+      <c r="D314" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="315" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:4" ht="44.25" x14ac:dyDescent="0.75">
       <c r="C315" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D315" s="8" t="s">
+      <c r="D315" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="316" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C316" t="s">
         <v>15</v>
       </c>
-      <c r="D316" t="s">
+      <c r="D316" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="317" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C317" t="s">
         <v>16</v>
       </c>
-      <c r="D317" t="s">
+      <c r="D317" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="318" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C318" t="s">
         <v>449</v>
       </c>
-      <c r="D318" t="s">
+      <c r="D318" s="10" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="319" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C319" t="s">
         <v>22</v>
       </c>
-      <c r="D319" t="s">
+      <c r="D319" s="10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="320" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C320" t="s">
         <v>25</v>
       </c>
-      <c r="D320" t="s">
+      <c r="D320" s="10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="321" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C321" t="s">
         <v>27</v>
       </c>
-      <c r="D321" t="s">
+      <c r="D321" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="322" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C322" t="s">
         <v>28</v>
       </c>
-      <c r="D322" t="s">
+      <c r="D322" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="323" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:4" x14ac:dyDescent="0.75">
       <c r="C323" t="s">
         <v>30</v>
       </c>
-      <c r="D323" t="s">
+      <c r="D323" s="10" t="s">
         <v>38</v>
       </c>
     </row>
